--- a/www/ig/fhir/ror/StructureDefinition-ror-measurereport.xlsx
+++ b/www/ig/fhir/ror/StructureDefinition-ror-measurereport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T09:54:01+00:00</t>
+    <t>2026-04-29T15:35:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
